--- a/docs/measured/excel-kara-2026-09-11.xlsx
+++ b/docs/measured/excel-kara-2026-09-11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\claude\C--WINDOWS-System32-WindowsPowerShell-v1-0\5b4e50e6-20a1-4af5-8ffb-8b6d6ca3f52b\scratchpad\gyaku\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\exally-wt-im\docs\measured\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{641951D3-93C5-416F-A7E0-9A8A156128A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF4ED5A-D1DF-4ACA-8DD3-89464232D89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{F07C1AA2-DD87-415E-952D-A46F472EF0C1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{76FD251A-D86B-478A-8C95-196ED8D4D513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCF28F-84C9-4691-ACFC-B95C04EBC611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF67EC7E-D27B-4C79-806E-A5796109D105}">
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
